--- a/tests/integration_workspace/review_classification_full/output/price_change_report.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/price_change_report.xlsx
@@ -489,6 +489,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>35.5</v>
       </c>
@@ -497,12 +502,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">

--- a/tests/integration_workspace/review_classification_full/output/price_change_report.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/price_change_report.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
